--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СИЙД ЕКСПРЕС ЕООД/СИЙД ЕКСПРЕС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СИЙД ЕКСПРЕС ЕООД/СИЙД ЕКСПРЕС ЕООД.xlsx
@@ -230,7 +230,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1474,7 +1474,7 @@
         <v>14</v>
       </c>
       <c r="D23" s="8">
-        <v>1.5971</v>
+        <v>1.597065</v>
       </c>
       <c r="E23" s="7">
         <v>7589.97</v>
@@ -1494,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="8">
-        <v>1.27</v>
+        <v>1.27003</v>
       </c>
       <c r="E24" s="7">
         <v>110.01</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="8">
-        <v>1.4097</v>
+        <v>1.409726</v>
       </c>
       <c r="E25" s="7">
         <v>29.28</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СИЙД ЕКСПРЕС ЕООД/СИЙД ЕКСПРЕС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СИЙД ЕКСПРЕС ЕООД/СИЙД ЕКСПРЕС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -622,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -635,13 +638,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -684,758 +687,812 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>57.4</v>
+        <v>57.398</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>1.51</v>
+        <v>1.499</v>
       </c>
       <c r="I2" s="1">
-        <v>86.67</v>
+        <v>1.509</v>
       </c>
       <c r="J2">
+        <v>86.61358199999999</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
-        <v>92.41</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>92.41078</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>296.45</v>
+        <v>296.447</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>1.51</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>447.64</v>
+        <v>1.509</v>
       </c>
       <c r="J3">
+        <v>447.338523</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.61</v>
       </c>
-      <c r="K3" s="1">
-        <v>477.28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="L3" s="1">
+        <v>477.27967</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>1.51</v>
+        <v>1.499</v>
       </c>
       <c r="I4" s="1">
-        <v>67.95</v>
+        <v>1.509</v>
       </c>
       <c r="J4">
+        <v>67.905</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.63</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>73.34999999999999</v>
       </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>1.51</v>
+        <v>1.499</v>
       </c>
       <c r="I5" s="1">
-        <v>77.01000000000001</v>
+        <v>1.509</v>
       </c>
       <c r="J5">
+        <v>76.959</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.66</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>84.66</v>
       </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46221</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>281.39</v>
+        <v>281.388</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>1.54</v>
+        <v>1.528</v>
       </c>
       <c r="I6" s="1">
-        <v>433.34</v>
+        <v>1.538</v>
       </c>
       <c r="J6">
+        <v>432.774744</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.65</v>
       </c>
-      <c r="K6" s="1">
-        <v>464.29</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="L6" s="1">
+        <v>464.2902</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46221</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>687.59</v>
+        <v>687.5890000000001</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>1.54</v>
+        <v>1.528</v>
       </c>
       <c r="I7" s="1">
-        <v>1058.89</v>
+        <v>1.538</v>
       </c>
       <c r="J7">
+        <v>1057.511882</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.68</v>
       </c>
-      <c r="K7" s="1">
-        <v>1155.15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="L7" s="1">
+        <v>1155.14952</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46221</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>242</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>1.54</v>
+        <v>1.528</v>
       </c>
       <c r="I8" s="1">
-        <v>372.68</v>
+        <v>1.538</v>
       </c>
       <c r="J8">
+        <v>372.196</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.68</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>406.56</v>
       </c>
-      <c r="L8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46222</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>11.09</v>
+        <v>11.092</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>1.4</v>
+        <v>1.379</v>
       </c>
       <c r="I9" s="1">
-        <v>15.53</v>
+        <v>1.399</v>
       </c>
       <c r="J9">
+        <v>15.517708</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.53</v>
       </c>
-      <c r="K9" s="1">
-        <v>16.97</v>
-      </c>
-      <c r="L9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="L9" s="1">
+        <v>16.97076</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46224</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>770.09</v>
+        <v>770.0890000000001</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>1.57</v>
+        <v>1.564</v>
       </c>
       <c r="I10" s="1">
-        <v>1209.04</v>
+        <v>1.574</v>
       </c>
       <c r="J10">
+        <v>1212.120086</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.68</v>
       </c>
-      <c r="K10" s="1">
-        <v>1293.75</v>
-      </c>
-      <c r="L10" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="1">
+        <v>1293.74952</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46225</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11">
         <v>270</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11">
-        <v>1.6</v>
+        <v>1.588</v>
       </c>
       <c r="I11" s="1">
-        <v>432</v>
+        <v>1.598</v>
       </c>
       <c r="J11">
+        <v>431.46</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.69</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>456.3</v>
       </c>
-      <c r="L11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46226</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>9.68</v>
+        <v>9.682</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>1.42</v>
+        <v>1.401</v>
       </c>
       <c r="I12" s="1">
-        <v>13.75</v>
+        <v>1.421</v>
       </c>
       <c r="J12">
+        <v>13.758122</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.54</v>
       </c>
-      <c r="K12" s="1">
-        <v>14.91</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="L12" s="1">
+        <v>14.91028</v>
+      </c>
+      <c r="M12" t="s">
+        <v>40</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46227</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>288.78</v>
+        <v>288.779</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13">
-        <v>1.63</v>
+        <v>1.619</v>
       </c>
       <c r="I13" s="1">
-        <v>470.71</v>
+        <v>1.629</v>
       </c>
       <c r="J13">
+        <v>470.420991</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.72</v>
       </c>
-      <c r="K13" s="1">
-        <v>496.7</v>
-      </c>
-      <c r="L13" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="1">
+        <v>496.69988</v>
+      </c>
+      <c r="M13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46228</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>86.62</v>
+        <v>86.622</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14">
         <v>1.27</v>
       </c>
       <c r="I14" s="1">
-        <v>110.01</v>
+        <v>1.27</v>
       </c>
       <c r="J14">
+        <v>110.00994</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.27</v>
       </c>
-      <c r="K14" s="1">
-        <v>110.01</v>
-      </c>
-      <c r="L14" t="s">
-        <v>41</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="1">
+        <v>110.00994</v>
+      </c>
+      <c r="M14" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46228</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>432.05</v>
+        <v>432.051</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15">
-        <v>1.63</v>
+        <v>1.619</v>
       </c>
       <c r="I15" s="1">
-        <v>704.24</v>
+        <v>1.629</v>
       </c>
       <c r="J15">
+        <v>703.8110789999999</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.77</v>
       </c>
-      <c r="K15" s="1">
-        <v>764.73</v>
-      </c>
-      <c r="L15" t="s">
-        <v>42</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="L15" s="1">
+        <v>764.73027</v>
+      </c>
+      <c r="M15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46231</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>288.38</v>
+        <v>288.383</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H16">
-        <v>1.66</v>
+        <v>1.653</v>
       </c>
       <c r="I16" s="1">
-        <v>478.71</v>
+        <v>1.663</v>
       </c>
       <c r="J16">
+        <v>479.580929</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.75</v>
       </c>
-      <c r="K16" s="1">
-        <v>504.66</v>
-      </c>
-      <c r="L16" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="L16" s="1">
+        <v>504.67025</v>
+      </c>
+      <c r="M16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46232</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17">
         <v>771.08</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H17">
-        <v>1.68</v>
+        <v>1.674</v>
       </c>
       <c r="I17" s="1">
-        <v>1295.41</v>
+        <v>1.684</v>
       </c>
       <c r="J17">
+        <v>1298.49872</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.75</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>1349.39</v>
       </c>
-      <c r="L17" t="s">
-        <v>44</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="M17" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46233</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>271.24</v>
+        <v>271.239</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18">
-        <v>1.68</v>
+        <v>1.674</v>
       </c>
       <c r="I18" s="1">
-        <v>455.68</v>
+        <v>1.684</v>
       </c>
       <c r="J18">
+        <v>456.766476</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.76</v>
       </c>
-      <c r="K18" s="1">
-        <v>477.38</v>
-      </c>
-      <c r="L18" t="s">
-        <v>45</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="L18" s="1">
+        <v>477.38064</v>
+      </c>
+      <c r="M18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1443,58 +1500,58 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15">
       <c r="A22" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="7">
-        <v>4752.45</v>
+        <v>4752.443</v>
       </c>
       <c r="C23" s="7">
         <v>14</v>
       </c>
       <c r="D23" s="8">
-        <v>1.597065</v>
+        <v>1.597906</v>
       </c>
       <c r="E23" s="7">
-        <v>7589.97</v>
+        <v>7593.96</v>
       </c>
       <c r="F23" s="7">
-        <v>8096.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>8096.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="7">
-        <v>86.62</v>
+        <v>86.622</v>
       </c>
       <c r="C24" s="7">
         <v>1</v>
       </c>
       <c r="D24" s="8">
-        <v>1.27003</v>
+        <v>1.27</v>
       </c>
       <c r="E24" s="7">
         <v>110.01</v>
@@ -1503,18 +1560,18 @@
         <v>110.01</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="7">
-        <v>20.77</v>
+        <v>20.774</v>
       </c>
       <c r="C25" s="7">
         <v>2</v>
       </c>
       <c r="D25" s="8">
-        <v>1.409726</v>
+        <v>1.409253</v>
       </c>
       <c r="E25" s="7">
         <v>29.28</v>
@@ -1523,22 +1580,22 @@
         <v>31.88</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="10">
-        <v>4859.84</v>
+        <v>4859.839</v>
       </c>
       <c r="C26" s="10">
         <v>17</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="10">
-        <v>7729.26</v>
+        <v>7733.25</v>
       </c>
       <c r="F26" s="10">
-        <v>8238.5</v>
+        <v>8238.51</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СИЙД ЕКСПРЕС ЕООД/СИЙД ЕКСПРЕС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СИЙД ЕКСПРЕС ЕООД/СИЙД ЕКСПРЕС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -231,9 +228,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -327,10 +324,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -638,13 +635,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -687,812 +684,758 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>57.398</v>
       </c>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2">
+        <v>1.509</v>
+      </c>
+      <c r="I2" s="1">
+        <v>86.614</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>92.411</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.509</v>
-      </c>
-      <c r="J2">
-        <v>86.61358199999999</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>92.41078</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>296.447</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.509</v>
       </c>
       <c r="I3" s="1">
-        <v>1.509</v>
+        <v>447.339</v>
       </c>
       <c r="J3">
-        <v>447.338523</v>
+        <v>1.61</v>
       </c>
       <c r="K3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L3" s="1">
-        <v>477.27967</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>477.28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>1.499</v>
+        <v>1.509</v>
       </c>
       <c r="I4" s="1">
-        <v>1.509</v>
+        <v>67.905</v>
       </c>
       <c r="J4">
-        <v>67.905</v>
+        <v>1.63</v>
       </c>
       <c r="K4" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L4" s="1">
         <v>73.34999999999999</v>
       </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.509</v>
       </c>
       <c r="I5" s="1">
-        <v>1.509</v>
+        <v>76.959</v>
       </c>
       <c r="J5">
-        <v>76.959</v>
+        <v>1.66</v>
       </c>
       <c r="K5" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="L5" s="1">
         <v>84.66</v>
       </c>
-      <c r="M5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46221</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>281.388</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>1.528</v>
+        <v>1.538</v>
       </c>
       <c r="I6" s="1">
-        <v>1.538</v>
+        <v>432.775</v>
       </c>
       <c r="J6">
-        <v>432.774744</v>
+        <v>1.65</v>
       </c>
       <c r="K6" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L6" s="1">
-        <v>464.2902</v>
-      </c>
-      <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>464.29</v>
+      </c>
+      <c r="L6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46221</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>687.5890000000001</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>1.528</v>
+        <v>1.538</v>
       </c>
       <c r="I7" s="1">
-        <v>1.538</v>
+        <v>1057.512</v>
       </c>
       <c r="J7">
-        <v>1057.511882</v>
+        <v>1.68</v>
       </c>
       <c r="K7" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1155.14952</v>
-      </c>
-      <c r="M7" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>1155.15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46221</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>242</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8">
-        <v>1.528</v>
+        <v>1.538</v>
       </c>
       <c r="I8" s="1">
-        <v>1.538</v>
+        <v>372.196</v>
       </c>
       <c r="J8">
-        <v>372.196</v>
+        <v>1.68</v>
       </c>
       <c r="K8" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L8" s="1">
         <v>406.56</v>
       </c>
-      <c r="M8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46222</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9">
         <v>11.092</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>1.379</v>
+        <v>1.399</v>
       </c>
       <c r="I9" s="1">
-        <v>1.399</v>
+        <v>15.518</v>
       </c>
       <c r="J9">
-        <v>15.517708</v>
+        <v>1.53</v>
       </c>
       <c r="K9" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L9" s="1">
-        <v>16.97076</v>
-      </c>
-      <c r="M9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>16.971</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46224</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
         <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
       </c>
       <c r="F10">
         <v>770.0890000000001</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10">
-        <v>1.564</v>
+        <v>1.574</v>
       </c>
       <c r="I10" s="1">
-        <v>1.574</v>
+        <v>1212.12</v>
       </c>
       <c r="J10">
-        <v>1212.120086</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1293.74952</v>
-      </c>
-      <c r="M10" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>1293.75</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46225</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11">
         <v>270</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11">
-        <v>1.588</v>
+        <v>1.598</v>
       </c>
       <c r="I11" s="1">
-        <v>1.598</v>
+        <v>431.46</v>
       </c>
       <c r="J11">
-        <v>431.46</v>
+        <v>1.69</v>
       </c>
       <c r="K11" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L11" s="1">
         <v>456.3</v>
       </c>
-      <c r="M11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46226</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12">
         <v>9.682</v>
       </c>
       <c r="G12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12">
-        <v>1.401</v>
+        <v>1.421</v>
       </c>
       <c r="I12" s="1">
-        <v>1.421</v>
+        <v>13.758</v>
       </c>
       <c r="J12">
-        <v>13.758122</v>
+        <v>1.54</v>
       </c>
       <c r="K12" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L12" s="1">
-        <v>14.91028</v>
-      </c>
-      <c r="M12" t="s">
-        <v>40</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>14.91</v>
+      </c>
+      <c r="L12" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46227</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13">
         <v>288.779</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13">
-        <v>1.619</v>
+        <v>1.629</v>
       </c>
       <c r="I13" s="1">
-        <v>1.629</v>
+        <v>470.421</v>
       </c>
       <c r="J13">
-        <v>470.420991</v>
+        <v>1.72</v>
       </c>
       <c r="K13" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L13" s="1">
-        <v>496.69988</v>
-      </c>
-      <c r="M13" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>496.7</v>
+      </c>
+      <c r="L13" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46228</v>
       </c>
       <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14">
         <v>86.622</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H14">
         <v>1.27</v>
       </c>
       <c r="I14" s="1">
+        <v>110.01</v>
+      </c>
+      <c r="J14">
         <v>1.27</v>
       </c>
-      <c r="J14">
-        <v>110.00994</v>
-      </c>
       <c r="K14" s="1">
-        <v>1.27</v>
-      </c>
-      <c r="L14" s="1">
-        <v>110.00994</v>
-      </c>
-      <c r="M14" t="s">
-        <v>42</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>110.01</v>
+      </c>
+      <c r="L14" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46228</v>
       </c>
       <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15">
         <v>432.051</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15">
-        <v>1.619</v>
+        <v>1.629</v>
       </c>
       <c r="I15" s="1">
-        <v>1.629</v>
+        <v>703.811</v>
       </c>
       <c r="J15">
-        <v>703.8110789999999</v>
+        <v>1.77</v>
       </c>
       <c r="K15" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L15" s="1">
-        <v>764.73027</v>
-      </c>
-      <c r="M15" t="s">
-        <v>43</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>764.73</v>
+      </c>
+      <c r="L15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46231</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16">
         <v>288.383</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16">
-        <v>1.653</v>
+        <v>1.663</v>
       </c>
       <c r="I16" s="1">
-        <v>1.663</v>
+        <v>479.581</v>
       </c>
       <c r="J16">
-        <v>479.580929</v>
+        <v>1.75</v>
       </c>
       <c r="K16" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L16" s="1">
-        <v>504.67025</v>
-      </c>
-      <c r="M16" t="s">
-        <v>44</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>504.67</v>
+      </c>
+      <c r="L16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46232</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
         <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>26</v>
       </c>
       <c r="F17">
         <v>771.08</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>1.674</v>
+        <v>1.684</v>
       </c>
       <c r="I17" s="1">
-        <v>1.684</v>
+        <v>1298.499</v>
       </c>
       <c r="J17">
-        <v>1298.49872</v>
+        <v>1.75</v>
       </c>
       <c r="K17" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L17" s="1">
         <v>1349.39</v>
       </c>
-      <c r="M17" t="s">
-        <v>45</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="L17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46233</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18">
         <v>271.239</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18">
-        <v>1.674</v>
+        <v>1.684</v>
       </c>
       <c r="I18" s="1">
-        <v>1.684</v>
+        <v>456.766</v>
       </c>
       <c r="J18">
-        <v>456.766476</v>
+        <v>1.76</v>
       </c>
       <c r="K18" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L18" s="1">
-        <v>477.38064</v>
-      </c>
-      <c r="M18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
+        <v>477.381</v>
+      </c>
+      <c r="L18" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="4" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1500,89 +1443,89 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:14">
       <c r="A22" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="E22" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="7">
         <v>4752.443</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>14</v>
       </c>
       <c r="D23" s="8">
-        <v>1.597906</v>
-      </c>
-      <c r="E23" s="7">
-        <v>7593.96</v>
-      </c>
-      <c r="F23" s="7">
-        <v>8096.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>1.598</v>
+      </c>
+      <c r="E23" s="8">
+        <v>7593.958</v>
+      </c>
+      <c r="F23" s="8">
+        <v>8096.622</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="7">
         <v>86.622</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <v>1</v>
       </c>
       <c r="D24" s="8">
         <v>1.27</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <v>110.01</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <v>110.01</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:14">
       <c r="A25" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="7">
         <v>20.774</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <v>2</v>
       </c>
       <c r="D25" s="8">
-        <v>1.409253</v>
-      </c>
-      <c r="E25" s="7">
-        <v>29.28</v>
-      </c>
-      <c r="F25" s="7">
-        <v>31.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>1.409</v>
+      </c>
+      <c r="E25" s="8">
+        <v>29.276</v>
+      </c>
+      <c r="F25" s="8">
+        <v>31.881</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B26" s="10">
         <v>4859.839</v>
@@ -1592,10 +1535,10 @@
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="10">
-        <v>7733.25</v>
+        <v>7733.244</v>
       </c>
       <c r="F26" s="10">
-        <v>8238.51</v>
+        <v>8238.513000000001</v>
       </c>
     </row>
   </sheetData>
